--- a/docs/testing/PropertyOS_Alpha_Test_Cases.xlsx
+++ b/docs/testing/PropertyOS_Alpha_Test_Cases.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Test Cases'!$A$1:$I$102</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -123,6 +133,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -646,6 +659,23 @@
       <c r="A24" s="2" t="inlineStr">
         <is>
           <t>- N/A: not applicable at this milestone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Note on the Defect Log</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Row 2 (DEF-EXAMPLE) is a template only, shown in grey italics with Status = 'Example'. It illustrates the expected fields and is not a real defect — no software has been built or tested yet. Leave it in place as a formatting reference, or delete it once real defects are logged.</t>
         </is>
       </c>
     </row>
@@ -660,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I90"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1404,12 +1434,12 @@
     <row r="16" ht="60" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>TEN-01</t>
+          <t>OWN-01</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Tenancies</t>
+          <t>Ownership</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1419,12 +1449,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Record a current tenancy</t>
+          <t>Add individual ownership</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1434,12 +1464,12 @@
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>1. Add a tenancy with start date, monthly rent, payment day and tenant display name/initials.</t>
+          <t>1. Add an owner of type Individual with name, at 100% ownership.</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>- Tenancy is saved and shown as current on the property.</t>
+          <t>- Owner is saved and displayed as sole owner at 100%.</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
@@ -1451,12 +1481,12 @@
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>TEN-02</t>
+          <t>OWN-02</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Tenancies</t>
+          <t>Ownership</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1466,124 +1496,124 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Add joint ownership (two individuals)</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>1. Add two Individual owners, each at 50% ownership.</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>- Both owners are saved, displayed together, and percentages total 100%.</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>OWN-03</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Record a historical tenancy</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Add limited company ownership</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
         <is>
           <t>A property exists.</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t>1. Add a tenancy with an end date in the past.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="inlineStr">
-        <is>
-          <t>- Tenancy is saved and shown under tenancy history, not as current.</t>
-        </is>
-      </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>TEN-03</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>Tenancies</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t>1. Add an owner of type Limited Company with company name and registration number, at 100%.</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>- Owner saves correctly with company-specific fields and displays as a Limited Company owner.</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>OWN-04</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>No identity documents can be stored on a tenancy</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>On the tenancy create/edit form.</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>1. Inspect the tenancy form and any associated upload paths for an identity-document or Right to Rent evidence field.</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>- No such field or upload path exists anywhere in the Tenancies feature.</t>
-        </is>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>TEN-04</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>Tenancies</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>No bank details can be stored on a tenancy</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>On the tenancy create/edit form.</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>1. Inspect the tenancy form for bank account or sort-code fields.</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>- No such field exists anywhere in the Tenancies feature.</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Add trust ownership</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr">
+        <is>
+          <t>1. Add an owner of type Trust with trust name and trustee details, at 100%.</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>- Owner saves correctly with trust-specific fields and displays as a Trust owner.</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
@@ -1592,466 +1622,469 @@
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
+          <t>OWN-05</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Add partnership ownership</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>1. Add an owner of type Partnership with partnership name and partner details, at 100%.</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>- Owner saves correctly with partnership-specific fields and displays as a Partnership owner.</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>OWN-06</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Multiple owners with mixed entity types</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>1. Add an Individual owner at 60% and a Limited Company owner at 40% on the same property.</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>- Both owners are saved and displayed with their correct entity type and percentage.</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>OWN-07</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Ownership percentages must sum to 100%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>A property exists with at least one owner being added.</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>1. Attempt to save a set of owners whose percentages total less than 100% (e.g. 90%).
+2. Attempt to save a set totalling more than 100% (e.g. 110%).</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>- Both attempts are rejected with a clear validation error; the record is not saved until percentages sum to exactly 100%.</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>OWN-08</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>Edit ownership</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>A property has one or more owners.</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>1. Edit an existing owner's percentage, or replace an owner with a different entity.
+2. Save.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>- Changes persist, the percentage split is re-validated, and the property reflects the updated ownership.</t>
+        </is>
+      </c>
+      <c r="I23" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>OWN-09</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Entity-type-specific required fields</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>On the add-owner form.</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>1. Attempt to save a Limited Company owner without a company registration number.
+2. Attempt to save a Trust owner without trustee details.</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>- Form requires the entity-type-specific fields before the owner can be saved.</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>TEN-01</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Tenancies</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Record a current tenancy</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>1. Add a tenancy with start date, monthly rent, payment day and tenant display name/initials.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>- Tenancy is saved and shown as current on the property.</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>TEN-02</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Tenancies</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Record a historical tenancy</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>1. Add a tenancy with an end date in the past.</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>- Tenancy is saved and shown under tenancy history, not as current.</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TEN-03</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>Tenancies</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>No identity documents can be stored on a tenancy</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>On the tenancy create/edit form.</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>1. Inspect the tenancy form and any associated upload paths for an identity-document or Right to Rent evidence field.</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>- No such field or upload path exists anywhere in the Tenancies feature.</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>TEN-04</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Tenancies</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>No bank details can be stored on a tenancy</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>On the tenancy create/edit form.</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>1. Inspect the tenancy form for bank account or sort-code fields.</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>- No such field exists anywhere in the Tenancies feature.</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
           <t>TEN-05</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>Tenancies</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Tenant display name / initials only</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F29" s="8" t="inlineStr">
         <is>
           <t>A tenancy exists.</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>1. Enter a full tenant name.
 2. Confirm what is displayed and stored.</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>- Only a display name or initials are stored/shown — consistent with the minimisation principle.</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>TEN-06</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>Tenancies</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>Rent and payment day validation</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>On the tenancy form.</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>1. Enter a negative rent, non-numeric rent, or an invalid payment day (e.g. 32).</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>- Form rejects invalid values with a clear error.</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>COMP-01</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>Default requirement catalogue is correct</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>A fresh organisation.</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>1. Open the compliance requirement catalogue.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>- Catalogue includes exactly: Gas Safety, EPC, EICR, Deposit Protection, Right to Rent, Smoke Alarms, CO Alarms, Landlord Insurance.</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>COMP-02</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>Add a compliance record</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>A property exists.</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>1. Add a compliance record with category, issue date, expiry date, source document and notes.</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>- Record saves correctly and is linked to the property and document.</t>
-        </is>
-      </c>
-      <c r="I23" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>COMP-03</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Status: compliant</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>A compliance record with expiry well in the future.</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>1. View the record's calculated status.</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>- Status shows as 'compliant'.</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>COMP-04</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Status: due soon</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>A compliance record expiring within the due-soon window.</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>1. View the record's calculated status.</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>- Status shows as 'due soon'.</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>COMP-05</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Status: expired</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>A compliance record with an expiry date in the past.</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>1. View the record's calculated status.</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>- Status shows as 'expired'.</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>COMP-06</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Status: missing</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>A property with no record for a required category.</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>1. View the property's compliance summary.</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>- The category shows as 'missing'.</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>COMP-07</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Status: needs review</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>A compliance record flagged for manual review (e.g. unclear extracted date).</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>1. View the record's calculated status.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>- Status shows as 'needs review' and is not treated as compliant.</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>COMP-08</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Status: not applicable</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>A property where a category genuinely does not apply (e.g. no gas at the property).</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>1. Mark the category as not applicable.</t>
-        </is>
-      </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>- Status shows as 'not applicable' and is excluded from due/expired/missing counts.</t>
         </is>
       </c>
       <c r="I29" s="8" t="inlineStr">
@@ -2063,2893 +2096,3458 @@
     <row r="30" ht="60" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>TEN-06</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Tenancies</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>Rent and payment day validation</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>On the tenancy form.</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>1. Enter a negative rent, non-numeric rent, or an invalid payment day (e.g. 32).</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>- Form rejects invalid values with a clear error.</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>COMP-01</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Default requirement catalogue is correct</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>A fresh organisation.</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>1. Open the compliance requirement catalogue.</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>- Catalogue includes the nine default categories: Gas Safety, EPC, EICR, Deposit Protection, Right to Rent, Smoke Alarms, CO Alarms, Landlord Insurance and Fire Risk Assessment.</t>
+        </is>
+      </c>
+      <c r="I31" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>COMP-02</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Add a compliance record</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>A property exists.</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>1. Add a compliance record with category, issue date, expiry date, source document and notes.</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>- Record saves correctly and is linked to the property and document.</t>
+        </is>
+      </c>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>COMP-03</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>Status: compliant</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>A compliance record with expiry well in the future.</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>1. View the record's calculated status.</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>- Status shows as 'compliant'.</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>COMP-04</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Status: due soon</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>A compliance record expiring within the due-soon window.</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>1. View the record's calculated status.</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>- Status shows as 'due soon'.</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>COMP-05</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Status: expired</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>A compliance record with an expiry date in the past.</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>1. View the record's calculated status.</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>- Status shows as 'expired'.</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>COMP-06</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>Status: missing</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>A property with no record for a required category.</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>1. View the property's compliance summary.</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>- The category shows as 'missing'.</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>COMP-07</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Status: needs review</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>A compliance record flagged for manual review (e.g. unclear extracted date).</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>1. View the record's calculated status.</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>- Status shows as 'needs review' and is not treated as compliant.</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>COMP-08</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Status: not applicable</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>A property where a category genuinely does not apply (e.g. no gas at the property).</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>1. Mark the category as not applicable.</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>- Status shows as 'not applicable' and is excluded from due/expired/missing counts.</t>
+        </is>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
           <t>COMP-09</t>
         </is>
       </c>
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C39" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D30" s="8" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="E39" s="8" t="inlineStr">
         <is>
           <t>Portfolio-wide compliance table</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t>Multiple properties with mixed statuses.</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t>1. Open the Compliance screen.
 2. Apply status and category filters.</t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
         <is>
           <t>- Table shows accurate status per property/category and filters work correctly.</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>COMP-10</t>
         </is>
       </c>
-      <c r="B31" s="8" t="inlineStr">
+      <c r="B40" s="8" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E40" s="8" t="inlineStr">
         <is>
           <t>Completion date updates the record</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F40" s="8" t="inlineStr">
         <is>
           <t>A due-soon or expired compliance record.</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="G40" s="8" t="inlineStr">
         <is>
           <t>1. Record a completion with a new issue/expiry date.</t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>- Status recalculates correctly based on the new dates.</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>COMP-11</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Add a custom compliance requirement</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>An organisation has the default catalogue configured.</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
+        <is>
+          <t>1. Add a new custom requirement category not in the default list (e.g. 'Legionella Risk Assessment').</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>- Custom requirement is saved and appears in the catalogue for that organisation, and behaves identically to default categories for status calculation and Today rules.</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>COMP-12</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Custom requirements do not leak between organisations</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>Organisation A has added a custom requirement.</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>1. Sign in as a member of Organisation B.
+2. Open the compliance requirement catalogue.</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>- Organisation B's catalogue does not show Organisation A's custom requirement.</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>COMP-13</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Fire Risk Assessment tracks dates only, not authoring</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>A Fire Risk Assessment compliance record exists.</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
+        <is>
+          <t>1. Inspect what the Fire Risk Assessment record captures and any related functionality.</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>- PropertyOS tracks issue/expiry/review dates and evidence for Fire Risk Assessment like any other category; it does not author, generate or certify the assessment itself, consistent with the Alpha's exclusion of professional fire-risk-assessment authoring.</t>
+        </is>
+      </c>
+      <c r="I43" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>DOC-01</t>
         </is>
       </c>
-      <c r="B32" s="8" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D32" s="8" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E44" s="8" t="inlineStr">
         <is>
           <t>Upload a document</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F44" s="8" t="inlineStr">
         <is>
           <t>A property or compliance record exists.</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G44" s="8" t="inlineStr">
         <is>
           <t>1. Upload a file and associate it with a property, compliance record or maintenance issue.</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr">
         <is>
           <t>- Document uploads successfully and is linked to the correct record.</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>DOC-02</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Download a document — same organisation</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <t>A document exists in the user's organisation.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G45" s="6" t="inlineStr">
         <is>
           <t>1. Download the document.</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H45" s="6" t="inlineStr">
         <is>
           <t>- Document downloads correctly via an authorised link.</t>
         </is>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>DOC-03</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>Download a document — cross-organisation denied</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <t>A document exists in Organisation A; tester is a member of Organisation B.</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G46" s="6" t="inlineStr">
         <is>
           <t>1. Attempt to access the document via direct storage path or shared link guessing.</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H46" s="6" t="inlineStr">
         <is>
           <t>- Access is denied; no content is returned.</t>
         </is>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>DOC-04</t>
         </is>
       </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D35" s="8" t="inlineStr">
+      <c r="D47" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="E47" s="8" t="inlineStr">
         <is>
           <t>Manual classification</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F47" s="8" t="inlineStr">
         <is>
           <t>An uploaded, unclassified document.</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
+      <c r="G47" s="8" t="inlineStr">
         <is>
           <t>1. Manually classify the document type.</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H47" s="8" t="inlineStr">
         <is>
           <t>- Classification is saved and reflected in the document list.</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>DOC-05</t>
         </is>
       </c>
-      <c r="B36" s="8" t="inlineStr">
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E48" s="8" t="inlineStr">
         <is>
           <t>Processing and confirmation status</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F48" s="8" t="inlineStr">
         <is>
           <t>A document has been processed (Milestone 4) or is pending manual classification.</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
+      <c r="G48" s="8" t="inlineStr">
         <is>
           <t>1. View the document's processing/confirmation status.</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
         <is>
           <t>- Status accurately reflects whether the document's extracted data has been confirmed.</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>DOC-06</t>
         </is>
       </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C37" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E49" s="8" t="inlineStr">
         <is>
           <t>Extracted metadata stored separately from confirmed facts</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F49" s="8" t="inlineStr">
         <is>
           <t>A document has been processed by AI extraction.</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>1. Inspect extracted metadata before confirmation.
 2. Compare to the compliance record's confirmed fields.</t>
         </is>
       </c>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
         <is>
           <t>- Extracted metadata is held separately and does not alter confirmed operational facts until explicitly confirmed.</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
         <is>
           <t>DOC-07</t>
         </is>
       </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="C38" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E50" s="8" t="inlineStr">
         <is>
           <t>Storage path is organisation-prefixed</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F50" s="8" t="inlineStr">
         <is>
           <t>A document exists.</t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G50" s="8" t="inlineStr">
         <is>
           <t>1. Inspect the storage object path (via admin/dev tooling).</t>
         </is>
       </c>
-      <c r="H38" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>- Path is prefixed with the organisation ID, consistent with data/security requirements.</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>TASK-01</t>
         </is>
       </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C39" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D39" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E51" s="8" t="inlineStr">
         <is>
           <t>Create a manual task</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F51" s="8" t="inlineStr">
         <is>
           <t>A property exists.</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
+      <c r="G51" s="8" t="inlineStr">
         <is>
           <t>1. Create a task with priority and due date.</t>
         </is>
       </c>
-      <c r="H39" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>- Task is saved and appears in the task list with correct details.</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t>TASK-02</t>
         </is>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D40" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E52" s="8" t="inlineStr">
         <is>
           <t>System-generated task from compliance/Today</t>
         </is>
       </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="F52" s="8" t="inlineStr">
         <is>
           <t>A compliance record triggers a recommended action.</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G52" s="8" t="inlineStr">
         <is>
           <t>1. Trigger the condition (e.g. expiring compliance).
 2. Check the Tasks list.</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>- A system-generated task appears with the correct source, priority and due date.</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>TASK-03</t>
         </is>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E53" s="8" t="inlineStr">
         <is>
           <t>Complete a task</t>
         </is>
       </c>
-      <c r="F41" s="8" t="inlineStr">
+      <c r="F53" s="8" t="inlineStr">
         <is>
           <t>An open task exists.</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G53" s="8" t="inlineStr">
         <is>
           <t>1. Mark the task complete.</t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>- Task status updates to complete and a timeline event is written.</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t>TASK-04</t>
         </is>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C42" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E54" s="8" t="inlineStr">
         <is>
           <t>Cancel a task</t>
         </is>
       </c>
-      <c r="F42" s="8" t="inlineStr">
+      <c r="F54" s="8" t="inlineStr">
         <is>
           <t>An open task exists.</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="G54" s="8" t="inlineStr">
         <is>
           <t>1. Cancel the task.</t>
         </is>
       </c>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>- Task status updates to cancelled and is excluded from active/overdue counts.</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="60" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>TASK-05</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C43" s="8" t="inlineStr">
+      <c r="C55" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D55" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E55" s="8" t="inlineStr">
         <is>
           <t>Reopen a task</t>
         </is>
       </c>
-      <c r="F43" s="8" t="inlineStr">
+      <c r="F55" s="8" t="inlineStr">
         <is>
           <t>A completed or cancelled task exists.</t>
         </is>
       </c>
-      <c r="G43" s="8" t="inlineStr">
+      <c r="G55" s="8" t="inlineStr">
         <is>
           <t>1. Reopen the task.</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>- Task returns to an open/active status correctly.</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
         <is>
           <t>TASK-06</t>
         </is>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>Tasks</t>
         </is>
       </c>
-      <c r="C44" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D44" s="8" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>Filter tasks</t>
         </is>
       </c>
-      <c r="F44" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>Multiple tasks with mixed priority/status/due dates exist.</t>
         </is>
       </c>
-      <c r="G44" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>1. Apply filters on the Tasks screen.</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>- Filtered results are accurate.</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="60" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>MAINT-01</t>
         </is>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D45" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>Log a maintenance issue</t>
         </is>
       </c>
-      <c r="F45" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>A property exists.</t>
         </is>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>1. Create a maintenance issue with priority, contractor and cost estimate.</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>- Issue is saved with correct details and linked to the property.</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="60" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>MAINT-02</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B58" s="8" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E58" s="8" t="inlineStr">
         <is>
           <t>Update maintenance status and notes</t>
         </is>
       </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>A maintenance issue exists.</t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
+      <c r="G58" s="8" t="inlineStr">
         <is>
           <t>1. Progress the issue through its statuses, adding notes.</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H58" s="8" t="inlineStr">
         <is>
           <t>- Status and notes update correctly and are visible in the issue history.</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>MAINT-03</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Attach a document to a maintenance issue</t>
         </is>
       </c>
-      <c r="F47" s="8" t="inlineStr">
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>A maintenance issue exists.</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
+      <c r="G59" s="8" t="inlineStr">
         <is>
           <t>1. Upload/associate a supporting document (e.g. quote or invoice).</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>- Document is linked and visible from the maintenance issue.</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="60" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>MAINT-04</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>Maintenance</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E60" s="8" t="inlineStr">
         <is>
           <t>High-priority open maintenance appears on Today</t>
         </is>
       </c>
-      <c r="F48" s="8" t="inlineStr">
+      <c r="F60" s="8" t="inlineStr">
         <is>
           <t>A high or urgent-priority maintenance issue is open.</t>
         </is>
       </c>
-      <c r="G48" s="8" t="inlineStr">
+      <c r="G60" s="8" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H60" s="8" t="inlineStr">
         <is>
           <t>- A corresponding high-priority action appears, linked to the issue.</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
         <is>
           <t>TL-01</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C61" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D61" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>Timeline records key events</t>
         </is>
       </c>
-      <c r="F49" s="8" t="inlineStr">
+      <c r="F61" s="8" t="inlineStr">
         <is>
           <t>Various create/update/completion actions performed on a property.</t>
         </is>
       </c>
-      <c r="G49" s="8" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr">
         <is>
           <t>1. Perform: add compliance record, complete a task, log maintenance.
 2. Open the property timeline.</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
         <is>
           <t>- Each action appears as an append-only event with property, actor, source record and metadata.</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1">
-      <c r="A50" s="7" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>TL-02</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B62" s="8" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E62" s="8" t="inlineStr">
         <is>
           <t>Timeline is append-only</t>
         </is>
       </c>
-      <c r="F50" s="8" t="inlineStr">
+      <c r="F62" s="8" t="inlineStr">
         <is>
           <t>Timeline events exist.</t>
         </is>
       </c>
-      <c r="G50" s="8" t="inlineStr">
+      <c r="G62" s="8" t="inlineStr">
         <is>
           <t>1. Attempt to edit or delete a timeline event directly.</t>
         </is>
       </c>
-      <c r="H50" s="8" t="inlineStr">
+      <c r="H62" s="8" t="inlineStr">
         <is>
           <t>- Timeline events cannot be edited or deleted through normal use.</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
-      <c r="A51" s="7" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>TL-03</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>Timeline</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C63" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Timeline is not used as source of current state</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F63" s="8" t="inlineStr">
         <is>
           <t>A record is edited after a timeline event was written.</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G63" s="8" t="inlineStr">
         <is>
           <t>1. Edit a compliance record after its creation event is logged.
 2. Check that current compliance status reflects the latest edit, not the original event.</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>- Current state is read from the live record, not reconstructed from timeline events.</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="7" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>TODAY-01</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B64" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D52" s="8" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E64" s="8" t="inlineStr">
         <is>
           <t>Portfolio counts are accurate</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F64" s="8" t="inlineStr">
         <is>
           <t>A portfolio with a known number of properties/records.</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G64" s="8" t="inlineStr">
         <is>
           <t>1. Open Today.
 2. Compare displayed counts to the underlying data.</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H64" s="8" t="inlineStr">
         <is>
           <t>- Counts match exactly.</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>TODAY-02</t>
         </is>
       </c>
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>Compliance expiring in exactly 14 days → High action</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <t>A compliance record expiring in exactly 14 days from today.</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
+      <c r="G65" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H53" s="6" t="inlineStr">
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>- A High-priority action appears for this record.</t>
         </is>
       </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>TODAY-03</t>
         </is>
       </c>
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>Compliance expiring in 15 days → Medium action</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <t>A compliance record expiring in exactly 15 days from today.</t>
         </is>
       </c>
-      <c r="G54" s="6" t="inlineStr">
+      <c r="G66" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>- A Medium-priority action appears (boundary of the 15–45 day band).</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>TODAY-04</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>Compliance expiring in exactly 45 days → Medium action</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <t>A compliance record expiring in exactly 45 days from today.</t>
         </is>
       </c>
-      <c r="G55" s="6" t="inlineStr">
+      <c r="G67" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>- A Medium-priority action appears (still within the 15–45 day band).</t>
         </is>
       </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>TODAY-05</t>
         </is>
       </c>
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B68" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>Compliance expiring in 46 days → no action</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <t>A compliance record expiring in exactly 46 days from today.</t>
         </is>
       </c>
-      <c r="G56" s="6" t="inlineStr">
+      <c r="G68" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="H68" s="6" t="inlineStr">
         <is>
           <t>- No due-soon action appears for this record (outside the 45-day window).</t>
         </is>
       </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>TODAY-06</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>Compliance expired yesterday → Urgent action</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>A compliance record that expired 1 day ago.</t>
         </is>
       </c>
-      <c r="G57" s="6" t="inlineStr">
+      <c r="G69" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>- An Urgent action appears for this record.</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>TODAY-07</t>
         </is>
       </c>
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Compliance missing → High action</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>A property missing a required compliance category.</t>
         </is>
       </c>
-      <c r="G58" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>- A High-priority action appears prompting the missing record.</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="60" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>TODAY-08</t>
         </is>
       </c>
-      <c r="B59" s="8" t="inlineStr">
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C59" s="8" t="inlineStr">
+      <c r="C71" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D59" s="8" t="inlineStr">
+      <c r="D71" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>Overdue task priority is derived from the task</t>
         </is>
       </c>
-      <c r="F59" s="8" t="inlineStr">
+      <c r="F71" s="8" t="inlineStr">
         <is>
           <t>A task is overdue with a known priority.</t>
         </is>
       </c>
-      <c r="G59" s="8" t="inlineStr">
+      <c r="G71" s="8" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H59" s="8" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>- The action reflects the task's own priority, correctly ordered against other actions.</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="60" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>TODAY-09</t>
         </is>
       </c>
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>Tenancy ending in exactly 30 days → High review action</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>A tenancy ending in exactly 30 days.</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H60" s="6" t="inlineStr">
+      <c r="H72" s="6" t="inlineStr">
         <is>
           <t>- A High-priority review action appears.</t>
         </is>
       </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>TODAY-10</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>Tenancy ending in 31 days → Medium review action</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>A tenancy ending in exactly 31 days.</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H61" s="6" t="inlineStr">
+      <c r="H73" s="6" t="inlineStr">
         <is>
           <t>- A Medium-priority review action appears (boundary of 31–60 day band).</t>
         </is>
       </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>TODAY-11</t>
         </is>
       </c>
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Tenancy ending in exactly 60 days → Medium review action</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>A tenancy ending in exactly 60 days.</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H62" s="6" t="inlineStr">
+      <c r="H74" s="6" t="inlineStr">
         <is>
           <t>- A Medium-priority review action appears.</t>
         </is>
       </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>TODAY-12</t>
         </is>
       </c>
-      <c r="B63" s="8" t="inlineStr">
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C63" s="8" t="inlineStr">
+      <c r="C75" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D75" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>Tenancy ending in 61 days → no review action</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F75" s="8" t="inlineStr">
         <is>
           <t>A tenancy ending in exactly 61 days.</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G75" s="8" t="inlineStr">
         <is>
           <t>1. Open Today.</t>
         </is>
       </c>
-      <c r="H63" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>- No tenancy-ending action appears (outside the 60-day window).</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="7" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>TODAY-13</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B76" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C64" s="8" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D64" s="8" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="8" t="inlineStr">
+      <c r="E76" s="8" t="inlineStr">
         <is>
           <t>Recommendations ordered by urgency then due date</t>
         </is>
       </c>
-      <c r="F64" s="8" t="inlineStr">
+      <c r="F76" s="8" t="inlineStr">
         <is>
           <t>Multiple concurrent actions of different urgency and due dates exist.</t>
         </is>
       </c>
-      <c r="G64" s="8" t="inlineStr">
+      <c r="G76" s="8" t="inlineStr">
         <is>
           <t>1. Open Today.
 2. Inspect the order of recommended actions.</t>
         </is>
       </c>
-      <c r="H64" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>- Actions are ordered by urgency first, then due date, consistently.</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="60" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>TODAY-14</t>
         </is>
       </c>
-      <c r="B65" s="8" t="inlineStr">
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C65" s="8" t="inlineStr">
+      <c r="C77" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D65" s="8" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="8" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>Each recommendation has full context</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>Any recommended action.</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
+      <c r="G77" s="8" t="inlineStr">
         <is>
           <t>1. Inspect a recommended action's fields.</t>
         </is>
       </c>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>- Property, source type, source record, reason, due date and a working deep link are all present.</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>TODAY-15</t>
         </is>
       </c>
-      <c r="B66" s="8" t="inlineStr">
+      <c r="B78" s="8" t="inlineStr">
         <is>
           <t>Today</t>
         </is>
       </c>
-      <c r="C66" s="8" t="inlineStr">
+      <c r="C78" s="8" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D66" s="8" t="inlineStr">
+      <c r="D78" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="8" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>Timezone / midnight boundary handling</t>
         </is>
       </c>
-      <c r="F66" s="8" t="inlineStr">
+      <c r="F78" s="8" t="inlineStr">
         <is>
           <t>A record whose expiry falls at a date boundary relative to server/UK time.</t>
         </is>
       </c>
-      <c r="G66" s="8" t="inlineStr">
+      <c r="G78" s="8" t="inlineStr">
         <is>
           <t>1. Test around midnight UK time (or with server clock adjusted) whether the day-count changes at the correct moment.</t>
         </is>
       </c>
-      <c r="H66" s="8" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>- Day counts and thresholds change at UK midnight, not UTC midnight or another timezone's boundary.</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="60" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>EXP-01</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="C67" s="8" t="inlineStr">
+      <c r="C79" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D67" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>Export as JSON</t>
         </is>
       </c>
-      <c r="F67" s="8" t="inlineStr">
+      <c r="F79" s="8" t="inlineStr">
         <is>
           <t>An organisation with populated data across all feature areas.</t>
         </is>
       </c>
-      <c r="G67" s="8" t="inlineStr">
+      <c r="G79" s="8" t="inlineStr">
         <is>
           <t>1. Trigger export in JSON format.
 2. Inspect the file.</t>
         </is>
       </c>
-      <c r="H67" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>- Export contains complete, correctly structured data for the organisation only.</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
         <is>
           <t>EXP-02</t>
         </is>
       </c>
-      <c r="B68" s="8" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="C68" s="8" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D68" s="8" t="inlineStr">
+      <c r="D80" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E80" s="8" t="inlineStr">
         <is>
           <t>Export as CSV</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
+      <c r="F80" s="8" t="inlineStr">
         <is>
           <t>An organisation with populated data.</t>
         </is>
       </c>
-      <c r="G68" s="8" t="inlineStr">
+      <c r="G80" s="8" t="inlineStr">
         <is>
           <t>1. Trigger export in CSV format.
 2. Open in a spreadsheet tool.</t>
         </is>
       </c>
-      <c r="H68" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>- Export is valid CSV with correct columns and values per record type.</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>EXP-03</t>
         </is>
       </c>
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
+      <c r="D81" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>Export is organisation-scoped</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>Two organisations with data.</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>1. Export data as a member of Organisation A.</t>
         </is>
       </c>
-      <c r="H69" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>- Export contains only Organisation A's data — nothing from Organisation B.</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1">
+      <c r="A82" s="7" t="inlineStr">
         <is>
           <t>EXP-04</t>
         </is>
       </c>
-      <c r="B70" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>Export</t>
         </is>
       </c>
-      <c r="C70" s="8" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D70" s="8" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E82" s="8" t="inlineStr">
         <is>
           <t>Documents are exported via separate authorised links</t>
         </is>
       </c>
-      <c r="F70" s="8" t="inlineStr">
+      <c r="F82" s="8" t="inlineStr">
         <is>
           <t>An organisation with documents.</t>
         </is>
       </c>
-      <c r="G70" s="8" t="inlineStr">
+      <c r="G82" s="8" t="inlineStr">
         <is>
           <t>1. Run the export and inspect how documents are referenced.</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>- Documents are not embedded in the structured export; separate authorised download links are provided instead.</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
         <is>
           <t>SEC-01</t>
         </is>
       </c>
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="D71" s="6" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>RLS denies cross-organisation SELECT</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>Two organisations with data; direct DB/API access available for testing.</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>1. As a member of Organisation A, attempt to query records belonging to Organisation B directly (API/DB client).</t>
         </is>
       </c>
-      <c r="H71" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>- Zero rows returned; access denied at the RLS layer, not just hidden in the UI.</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="60" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>SEC-02</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>RLS denies cross-organisation INSERT/UPDATE/DELETE</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>Two organisations with data.</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>1. As a member of Organisation A, attempt to insert, update or delete a record with Organisation B's organisation_id.</t>
         </is>
       </c>
-      <c r="H72" s="6" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>- Operation is rejected by RLS.</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="60" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>SEC-03</t>
         </is>
       </c>
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>No secrets shipped in the Flutter client</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>A built Flutter Web client.</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>1. Inspect client bundle/network traffic for OpenAI API keys or Supabase service-role keys.</t>
         </is>
       </c>
-      <c r="H73" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>- No such secret is present anywhere in client-side code or requests.</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>SEC-04</t>
         </is>
       </c>
-      <c r="B74" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C74" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D74" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E86" s="8" t="inlineStr">
         <is>
           <t>Archived records remain recoverable and excluded from normal views</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
+      <c r="F86" s="8" t="inlineStr">
         <is>
           <t>An archived property or record.</t>
         </is>
       </c>
-      <c r="G74" s="8" t="inlineStr">
+      <c r="G86" s="8" t="inlineStr">
         <is>
           <t>1. Check default views.
 2. Check an admin/recovery view.</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>- Archived records are hidden from normal views but retrievable where intended.</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>SEC-05</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C75" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E87" s="8" t="inlineStr">
         <is>
           <t>Audit fields are present</t>
         </is>
       </c>
-      <c r="F75" s="8" t="inlineStr">
+      <c r="F87" s="8" t="inlineStr">
         <is>
           <t>Any record.</t>
         </is>
       </c>
-      <c r="G75" s="8" t="inlineStr">
+      <c r="G87" s="8" t="inlineStr">
         <is>
           <t>1. Inspect a record's metadata.</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>- created_at, updated_at and actor (where appropriate) are recorded correctly.</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>SEC-06</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Logs do not contain sensitive data</t>
         </is>
       </c>
-      <c r="F76" s="8" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>Application logs after normal use including document uploads.</t>
         </is>
       </c>
-      <c r="G76" s="8" t="inlineStr">
+      <c r="G88" s="8" t="inlineStr">
         <is>
           <t>1. Inspect logs generated during document upload and compliance record creation.</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>- Logs contain no document contents or personal data.</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="60" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>SEC-07</t>
         </is>
       </c>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>Security / RLS</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Backup, export and deletion behaviour</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>Production-like data before external landlord invites.</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>1. Test a full backup/restore cycle.
 2. Test export.
 3. Test account/organisation deletion.</t>
         </is>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>- All three behave correctly and safely before any external user is invited.</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>AI-01</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B90" s="8" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C90" s="8" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D90" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>AI suggests document type and property</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="F90" s="8" t="inlineStr">
         <is>
           <t>A document is uploaded for AI processing.</t>
         </is>
       </c>
-      <c r="G78" s="8" t="inlineStr">
+      <c r="G90" s="8" t="inlineStr">
         <is>
           <t>1. Upload a document and trigger extraction.</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
         <is>
           <t>- A suggested document type and property are proposed, not auto-applied.</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>AI-02</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C91" s="8" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D91" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>AI extracts dates and references with confidence</t>
         </is>
       </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="F91" s="8" t="inlineStr">
         <is>
           <t>A document with clear certificate dates is processed.</t>
         </is>
       </c>
-      <c r="G79" s="8" t="inlineStr">
+      <c r="G91" s="8" t="inlineStr">
         <is>
           <t>1. Trigger extraction.</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H91" s="8" t="inlineStr">
         <is>
           <t>- Issue/expiry/review dates and certificate/policy references are proposed, each with a confidence score and supporting source text.</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="60" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>AI-03</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
+      <c r="D92" s="6" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>AI cannot silently overwrite a confirmed fact</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>A compliance record already has confirmed dates.</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>1. Upload a new document with conflicting dates and run extraction.</t>
         </is>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H92" s="6" t="inlineStr">
         <is>
           <t>- The confirmed record is not changed until a human explicitly confirms the new values.</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="60" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>AI-04</t>
         </is>
       </c>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D93" s="6" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>AI cannot generate a status without deterministic rules</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>A processed document with extracted dates.</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>1. Inspect how compliance status is set after extraction.</t>
         </is>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H93" s="6" t="inlineStr">
         <is>
           <t>- Status is only ever set by the deterministic rules engine, never directly by the AI extraction step.</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="60" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="60" customHeight="1">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>AI-05</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>AI cannot expose one organisation's data to another</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>Two organisations each with documents pending extraction.</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>1. Trigger extraction for Organisation A's document.
 2. Inspect the function's inputs/context for any Organisation B data.</t>
         </is>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H94" s="6" t="inlineStr">
         <is>
           <t>- Extraction context is limited strictly to the requesting organisation's own document.</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="60" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="7" t="inlineStr">
         <is>
           <t>AI-06</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>AI Boundary</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>AI never certifies compliance</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F95" s="8" t="inlineStr">
         <is>
           <t>Any AI-assisted suggestion.</t>
         </is>
       </c>
-      <c r="G83" s="8" t="inlineStr">
+      <c r="G95" s="8" t="inlineStr">
         <is>
           <t>1. Review the language used in AI suggestions and confirmations.</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>- Suggestions are framed as proposals requiring confirmation; nothing claims to certify legal compliance.</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="60" customHeight="1">
-      <c r="A84" s="7" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1">
+      <c r="A96" s="7" t="inlineStr">
         <is>
           <t>NFR-01</t>
         </is>
       </c>
-      <c r="B84" s="8" t="inlineStr">
+      <c r="B96" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C84" s="8" t="inlineStr">
+      <c r="C96" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D84" s="8" t="inlineStr">
+      <c r="D96" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E96" s="8" t="inlineStr">
         <is>
           <t>UK date format throughout</t>
         </is>
       </c>
-      <c r="F84" s="8" t="inlineStr">
+      <c r="F96" s="8" t="inlineStr">
         <is>
           <t>Any screen showing dates.</t>
         </is>
       </c>
-      <c r="G84" s="8" t="inlineStr">
+      <c r="G96" s="8" t="inlineStr">
         <is>
           <t>1. Inspect dates across Today, Properties, Compliance, Tasks, Maintenance.</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>- Dates are shown in UK format (DD/MM/YYYY or equivalent UK convention) everywhere.</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="60" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>NFR-02</t>
         </is>
       </c>
-      <c r="B85" s="8" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C85" s="8" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D85" s="8" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E97" s="8" t="inlineStr">
         <is>
           <t>Currency shown as GBP</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
+      <c r="F97" s="8" t="inlineStr">
         <is>
           <t>Any screen showing money (rent, cost estimate).</t>
         </is>
       </c>
-      <c r="G85" s="8" t="inlineStr">
+      <c r="G97" s="8" t="inlineStr">
         <is>
           <t>1. Inspect rent and maintenance cost fields.</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>- Values are shown in GBP with correct formatting.</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="60" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1">
+      <c r="A98" s="7" t="inlineStr">
         <is>
           <t>NFR-03</t>
         </is>
       </c>
-      <c r="B86" s="8" t="inlineStr">
+      <c r="B98" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C86" s="8" t="inlineStr">
+      <c r="C98" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D86" s="8" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E98" s="8" t="inlineStr">
         <is>
           <t>UK terminology used consistently</t>
         </is>
       </c>
-      <c r="F86" s="8" t="inlineStr">
+      <c r="F98" s="8" t="inlineStr">
         <is>
           <t>Any screen.</t>
         </is>
       </c>
-      <c r="G86" s="8" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr">
         <is>
           <t>1. Review copy for terminology (e.g. 'landlord', 'tenancy', 'EICR', 'EPC').</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>- Terminology matches UK lettings conventions throughout, no US equivalents.</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="60" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>NFR-04</t>
         </is>
       </c>
-      <c r="B87" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C87" s="8" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E99" s="8" t="inlineStr">
         <is>
           <t>Keyboard-only navigation</t>
         </is>
       </c>
-      <c r="F87" s="8" t="inlineStr">
+      <c r="F99" s="8" t="inlineStr">
         <is>
           <t>Any core screen.</t>
         </is>
       </c>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="G99" s="8" t="inlineStr">
         <is>
           <t>1. Navigate and operate each core screen using only the keyboard (tab, enter, arrow keys).</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>- All interactive elements are reachable and operable without a mouse.</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="60" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>NFR-05</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C88" s="8" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D88" s="8" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="8" t="inlineStr">
+      <c r="E100" s="8" t="inlineStr">
         <is>
           <t>Responsive at common widths</t>
         </is>
       </c>
-      <c r="F88" s="8" t="inlineStr">
+      <c r="F100" s="8" t="inlineStr">
         <is>
           <t>Any core screen.</t>
         </is>
       </c>
-      <c r="G88" s="8" t="inlineStr">
+      <c r="G100" s="8" t="inlineStr">
         <is>
           <t>1. View each core screen at mobile, tablet and desktop widths.</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>- Layout remains usable with no broken or clipped content at any of the three widths.</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="7" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>NFR-06</t>
         </is>
       </c>
-      <c r="B89" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C89" s="8" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="D89" s="8" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="8" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>Errors give recovery guidance without leaking internals</t>
         </is>
       </c>
-      <c r="F89" s="8" t="inlineStr">
+      <c r="F101" s="8" t="inlineStr">
         <is>
           <t>A triggerable error condition (e.g. failed upload, network error).</t>
         </is>
       </c>
-      <c r="G89" s="8" t="inlineStr">
+      <c r="G101" s="8" t="inlineStr">
         <is>
           <t>1. Force an error condition.</t>
         </is>
       </c>
-      <c r="H89" s="8" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>- User sees a clear, actionable message; no stack trace, SQL, or internal identifiers are exposed.</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="60" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>NFR-07</t>
         </is>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B102" s="8" t="inlineStr">
         <is>
           <t>Non-functional</t>
         </is>
       </c>
-      <c r="C90" s="8" t="inlineStr">
+      <c r="C102" s="8" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="D90" s="8" t="inlineStr">
+      <c r="D102" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="8" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>Seed data is fictional and clearly separated</t>
         </is>
       </c>
-      <c r="F90" s="8" t="inlineStr">
+      <c r="F102" s="8" t="inlineStr">
         <is>
           <t>Development/test environment.</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
+      <c r="G102" s="8" t="inlineStr">
         <is>
           <t>1. Inspect seed data used for testing.</t>
         </is>
       </c>
-      <c r="H90" s="8" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>- Seed data is clearly fictional and never mixed with or mistaken for production data.</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I90"/>
+  <autoFilter ref="A1:I102"/>
   <dataValidations count="3">
-    <dataValidation sqref="I2:I90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,In progress,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Blocker,Critical,High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C102" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"M1,M2,M3,M4,M5,M2+,All"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5037,410 +5635,414 @@
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
-        <is>
-          <t>DEF-001</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>DEF-EXAMPLE</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>TODAY-06</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" s="9" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
+      <c r="E2" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
-        <is>
-          <t>Expired compliance not shown as Urgent on Today</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>[TEMPLATE EXAMPLE — not a real defect] Expired compliance not shown as Urgent on Today</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>1. Create Gas Safety record expired 1 day ago.
 2. Open Today.</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Expected: Urgent action shown.
 Actual: no action appears.</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="K2" s="8" t="inlineStr"/>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="n"/>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="n"/>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="9" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n"/>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n"/>
-      <c r="B6" s="9" t="n"/>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="10" t="n"/>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="10" t="n"/>
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="10" t="n"/>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="10" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="10" t="n"/>
+      <c r="J7" s="10" t="n"/>
+      <c r="K7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="10" t="n"/>
+      <c r="C8" s="10" t="n"/>
+      <c r="D8" s="10" t="n"/>
+      <c r="E8" s="10" t="n"/>
+      <c r="F8" s="10" t="n"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="10" t="n"/>
+      <c r="J8" s="10" t="n"/>
+      <c r="K8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="n"/>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="10" t="n"/>
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="10" t="n"/>
+      <c r="E9" s="10" t="n"/>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="10" t="n"/>
+      <c r="J9" s="10" t="n"/>
+      <c r="K9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="n"/>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="10" t="n"/>
+      <c r="C11" s="10" t="n"/>
+      <c r="D11" s="10" t="n"/>
+      <c r="E11" s="10" t="n"/>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="10" t="n"/>
+      <c r="J11" s="10" t="n"/>
+      <c r="K11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
+      <c r="A12" s="10" t="n"/>
+      <c r="B12" s="10" t="n"/>
+      <c r="C12" s="10" t="n"/>
+      <c r="D12" s="10" t="n"/>
+      <c r="E12" s="10" t="n"/>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="10" t="n"/>
+      <c r="J12" s="10" t="n"/>
+      <c r="K12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+      <c r="A13" s="10" t="n"/>
+      <c r="B13" s="10" t="n"/>
+      <c r="C13" s="10" t="n"/>
+      <c r="D13" s="10" t="n"/>
+      <c r="E13" s="10" t="n"/>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="10" t="n"/>
+      <c r="J13" s="10" t="n"/>
+      <c r="K13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="9" t="n"/>
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="10" t="n"/>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+      <c r="I15" s="10" t="n"/>
+      <c r="J15" s="10" t="n"/>
+      <c r="K15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="9" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="10" t="n"/>
+      <c r="F16" s="10" t="n"/>
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="10" t="n"/>
+      <c r="K16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="9" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="10" t="n"/>
+      <c r="F17" s="10" t="n"/>
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n"/>
+      <c r="I17" s="10" t="n"/>
+      <c r="J17" s="10" t="n"/>
+      <c r="K17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="n"/>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="9" t="n"/>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="10" t="n"/>
+      <c r="F18" s="10" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n"/>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="10" t="n"/>
+      <c r="F19" s="10" t="n"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n"/>
+      <c r="I19" s="10" t="n"/>
+      <c r="J19" s="10" t="n"/>
+      <c r="K19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n"/>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="9" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="9" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="9" t="n"/>
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="10" t="n"/>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="10" t="n"/>
+      <c r="K21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="10" t="n"/>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="9" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="10" t="n"/>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="10" t="n"/>
+      <c r="K24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="9" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="10" t="n"/>
+      <c r="K25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n"/>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="9" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="10" t="n"/>
+      <c r="F26" s="10" t="n"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n"/>
+      <c r="I26" s="10" t="n"/>
+      <c r="J26" s="10" t="n"/>
+      <c r="K26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="9" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="9" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n"/>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="n"/>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="9" t="n"/>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="10" t="n"/>
+      <c r="H28" s="10" t="n"/>
+      <c r="I28" s="10" t="n"/>
+      <c r="J28" s="10" t="n"/>
+      <c r="K28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="n"/>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-      <c r="K29" s="9" t="n"/>
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+      <c r="I29" s="10" t="n"/>
+      <c r="J29" s="10" t="n"/>
+      <c r="K29" s="10" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="2">
@@ -5448,7 +6050,7 @@
       <formula1>"Blocker,Critical,Major,Minor"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"New,Confirmed,Fixed,Retested,Closed,Rejected,Deferred"</formula1>
+      <formula1>"New,Confirmed,Fixed,Retested,Closed,Rejected,Deferred,Example"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
